--- a/project/HW3/22127410/22127410_DataGeneration_10/22127410_TestCase.xlsx
+++ b/project/HW3/22127410/22127410_DataGeneration_10/22127410_TestCase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thanhthuy/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5982BA75-7237-E546-9771-AA813D797D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F9935B-4528-E34D-85EA-BACF05A1860E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="256">
   <si>
     <t>ID</t>
   </si>
@@ -208,560 +208,758 @@
     <t>TC_024</t>
   </si>
   <si>
-    <t>A logged-in user with items in their cart wants to complete a purchase on The ToolShop. They review the cart, enter shipping information, select a payment method, and confirm the order. The system processes the payment, updates inventory, and sends a confirmation email.</t>
-  </si>
-  <si>
-    <t>Checkout</t>
-  </si>
-  <si>
-    <t>Cao Uyen Nhi</t>
-  </si>
-  <si>
-    <t>A new customer wants to create an account on The ToolShop to start shopping. They navigate to the Customer Registration page, fill in all the required fields—including first name, last name, date of birth, address, postcode, city, country, state, phone number, email address, and password—and click the “Register” button. The system validates all input fields, checks for unique email and phone number, stores the account information in the database if all entries are valid, and displays an appropriate success or error message to the user.</t>
-  </si>
-  <si>
-    <t>Customer Registration</t>
-  </si>
-  <si>
-    <t>Email already in database</t>
-  </si>
-  <si>
-    <t>Phone already in database</t>
-  </si>
-  <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Successful registration</t>
-  </si>
-  <si>
-    <t>User is on the registration page</t>
-  </si>
-  <si>
-    <t>All fields are filled correctly</t>
-  </si>
-  <si>
-    <t>1. Fill form
-2. Click Submit/Register</t>
-  </si>
-  <si>
-    <t>Success message displayed</t>
-  </si>
-  <si>
-    <t>Missing First Name</t>
-  </si>
-  <si>
-    <t>First Name is empty</t>
-  </si>
-  <si>
-    <t>Inline error, form not submitted</t>
-  </si>
-  <si>
-    <t>Missing Last Name</t>
-  </si>
-  <si>
-    <t>Last Name is empty</t>
-  </si>
-  <si>
-    <t>Missing Date of Birth</t>
-  </si>
-  <si>
-    <t>Date of Birth is empty</t>
-  </si>
-  <si>
-    <t>Underage user</t>
-  </si>
-  <si>
-    <t>Date of Birth &lt; 18 years</t>
-  </si>
-  <si>
-    <t>Error message displayed</t>
-  </si>
-  <si>
-    <t>Missing Address</t>
-  </si>
-  <si>
-    <t>Address is empty</t>
-  </si>
-  <si>
     <t>Inline error</t>
   </si>
   <si>
-    <t>Missing Postcode</t>
-  </si>
-  <si>
-    <t>Postcode is empty</t>
-  </si>
-  <si>
-    <t>Invalid Postcode</t>
-  </si>
-  <si>
-    <t>Alphabetic characters in postcode</t>
-  </si>
-  <si>
-    <t>Validation fails</t>
-  </si>
-  <si>
-    <t>Missing City</t>
-  </si>
-  <si>
-    <t>City is empty</t>
-  </si>
-  <si>
-    <t>Missing State</t>
-  </si>
-  <si>
-    <t>State is empty</t>
-  </si>
-  <si>
-    <t>Missing Country</t>
-  </si>
-  <si>
-    <t>Country not selected</t>
-  </si>
-  <si>
-    <t>Error shown</t>
-  </si>
-  <si>
-    <t>Missing Phone</t>
-  </si>
-  <si>
-    <t>Phone is empty</t>
-  </si>
-  <si>
-    <t>Invalid Phone Format</t>
-  </si>
-  <si>
-    <t>Phone has letters or invalid length</t>
-  </si>
-  <si>
-    <t>Missing Email</t>
-  </si>
-  <si>
-    <t>Email is empty</t>
-  </si>
-  <si>
-    <t>Invalid Email Format</t>
-  </si>
-  <si>
-    <t>Missing @ or domain</t>
-  </si>
-  <si>
-    <t>Duplicate Email</t>
-  </si>
-  <si>
-    <t>Missing Password</t>
-  </si>
-  <si>
-    <t>Password field is empty</t>
-  </si>
-  <si>
-    <t>Weak Password</t>
-  </si>
-  <si>
-    <t>Password &lt; 8 chars or lacks complexity</t>
-  </si>
-  <si>
-    <t>Duplicate Phone</t>
-  </si>
-  <si>
-    <t>Successful checkout</t>
-  </si>
-  <si>
-    <t>User is on the checkout page</t>
-  </si>
-  <si>
-    <t>Logged-in user completes all steps with valid data</t>
-  </si>
-  <si>
-    <t>1. Review cart
-2. Fill shipping
-3. Select payment
-4. Click Confirm</t>
-  </si>
-  <si>
-    <t>Order placed successfully</t>
-  </si>
-  <si>
-    <t>User not logged in</t>
-  </si>
-  <si>
-    <t>User attempts checkout without login</t>
-  </si>
-  <si>
-    <t>Cart is empty</t>
-  </si>
-  <si>
-    <t>No items in cart</t>
-  </si>
-  <si>
-    <t>Error: Cart is empty</t>
-  </si>
-  <si>
-    <t>Missing shipping info</t>
-  </si>
-  <si>
-    <t>Shipping address or phone is missing</t>
-  </si>
-  <si>
-    <t>Inline error, cannot submit</t>
-  </si>
-  <si>
-    <t>Invalid shipping info</t>
-  </si>
-  <si>
-    <t>Postcode or address format is invalid</t>
-  </si>
-  <si>
-    <t>Error message shown</t>
-  </si>
-  <si>
-    <t>No payment method selected</t>
-  </si>
-  <si>
-    <t>Payment method is not chosen</t>
-  </si>
-  <si>
-    <t>Address auto-fill via profile</t>
-  </si>
-  <si>
-    <t>User has saved address in profile</t>
-  </si>
-  <si>
-    <t>Checkout uses saved address automatically</t>
-  </si>
-  <si>
-    <t>1. Go to checkout
-2. Verify auto-fill
-3. Confirm order</t>
-  </si>
-  <si>
-    <t>Shipping address auto-filled correctly</t>
-  </si>
-  <si>
     <t>Feature</t>
   </si>
   <si>
     <t>Feature ID</t>
   </si>
   <si>
-    <t>Feature 01: Customer Registration</t>
-  </si>
-  <si>
-    <t>Feature 02: Checkout</t>
-  </si>
-  <si>
-    <t>Attempt registration with emoji input</t>
-  </si>
-  <si>
-    <t>Enter emoji in name or address fields</t>
-  </si>
-  <si>
-    <t>1. Fill form with emojis
+    <t>User Sign In</t>
+  </si>
+  <si>
+    <t>User Management</t>
+  </si>
+  <si>
+    <t>Feature 01: User Sign In</t>
+  </si>
+  <si>
+    <t>Luu Thanh Thuy</t>
+  </si>
+  <si>
+    <t>Unregistered email</t>
+  </si>
+  <si>
+    <t>Wrong password</t>
+  </si>
+  <si>
+    <t>Valid login - user role</t>
+  </si>
+  <si>
+    <t>Registered user</t>
+  </si>
+  <si>
+    <t>1. Go to /signin
+2. Enter user credentials
+3. Click Sign In</t>
+  </si>
+  <si>
+    <t>Redirect to /dashboard/user</t>
+  </si>
+  <si>
+    <t>Valid login - admin role</t>
+  </si>
+  <si>
+    <t>Registered admin</t>
+  </si>
+  <si>
+    <t>1. Enter admin credentials
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>Redirect to /dashboard/admin</t>
+  </si>
+  <si>
+    <t>Missing email</t>
+  </si>
+  <si>
+    <t>User on Sign In page</t>
+  </si>
+  <si>
+    <t>Email: (blank), Password: ValidPass123</t>
+  </si>
+  <si>
+    <t>Inline error: Email is required</t>
+  </si>
+  <si>
+    <t>Missing password</t>
+  </si>
+  <si>
+    <t>Email: user@example.com, Password: (blank)</t>
+  </si>
+  <si>
+    <t>Inline error: Password is required</t>
+  </si>
+  <si>
+    <t>Email without '@'</t>
+  </si>
+  <si>
+    <t>Email: userexample.com, Password: Password123</t>
+  </si>
+  <si>
+    <t>Inline error: Invalid email</t>
+  </si>
+  <si>
+    <t>Email with invalid domain</t>
+  </si>
+  <si>
+    <t>Email: user@.com, Password: Password123</t>
+  </si>
+  <si>
+    <t>User is registered</t>
+  </si>
+  <si>
+    <t>Email: user1@example.com, Password: WrongPass</t>
+  </si>
+  <si>
+    <t>Error: Incorrect password</t>
+  </si>
+  <si>
+    <t>Email not in database</t>
+  </si>
+  <si>
+    <t>Email: fakeuser@example.com, Password: ValidPass123</t>
+  </si>
+  <si>
+    <t>Error: No account found</t>
+  </si>
+  <si>
+    <t>Email case sensitivity</t>
+  </si>
+  <si>
+    <t>User email is lowercase</t>
+  </si>
+  <si>
+    <t>Email: USER1@example.com, Password: User@123</t>
+  </si>
+  <si>
+    <t>Email with trailing spaces</t>
+  </si>
+  <si>
+    <t>User email has whitespace</t>
+  </si>
+  <si>
+    <t>Email: user1@example.com  , Password: User@123</t>
+  </si>
+  <si>
+    <t>Password with leading spaces</t>
+  </si>
+  <si>
+    <t>Valid credentials</t>
+  </si>
+  <si>
+    <t>Email: user1@example.com, Password:   User@123</t>
+  </si>
+  <si>
+    <t>SQL injection attempt</t>
+  </si>
+  <si>
+    <t>Email: ' OR 1=1 --, Password: anything</t>
+  </si>
+  <si>
+    <t>Cross-site scripting attempt</t>
+  </si>
+  <si>
+    <t>Email: &lt;script&gt;, Password: anything</t>
+  </si>
+  <si>
+    <t>Multiple failed attempts</t>
+  </si>
+  <si>
+    <t>User tries multiple times</t>
+  </si>
+  <si>
+    <t>Invalid credentials</t>
+  </si>
+  <si>
+    <t>Try invalid login 5 times</t>
+  </si>
+  <si>
+    <t>Rate limit or delay triggered</t>
+  </si>
+  <si>
+    <t>Inactive user account</t>
+  </si>
+  <si>
+    <t>User exists but inactive</t>
+  </si>
+  <si>
+    <t>Email: inactive@example.com, Password: Valid123</t>
+  </si>
+  <si>
+    <t>Error: Account inactive</t>
+  </si>
+  <si>
+    <t>HTML in email input</t>
+  </si>
+  <si>
+    <t>Email: &lt;b&gt;user@example.com&lt;/b&gt;, Password: Password123</t>
+  </si>
+  <si>
+    <t>Excessively long email</t>
+  </si>
+  <si>
+    <t>Inline error or truncated</t>
+  </si>
+  <si>
+    <t>Copy-paste email</t>
+  </si>
+  <si>
+    <t>Valid user</t>
+  </si>
+  <si>
+    <t>Email pasted: user1@example.com</t>
+  </si>
+  <si>
+    <t>Password copy-paste</t>
+  </si>
+  <si>
+    <t>Password pasted: User@123</t>
+  </si>
+  <si>
+    <t>Toggle password visibility</t>
+  </si>
+  <si>
+    <t>User on Sign In form</t>
+  </si>
+  <si>
+    <t>Click show password icon</t>
+  </si>
+  <si>
+    <t>Login works</t>
+  </si>
+  <si>
+    <t>Press Enter to submit</t>
+  </si>
+  <si>
+    <t>User fills form</t>
+  </si>
+  <si>
+    <t>Fill form
+Press Enter</t>
+  </si>
+  <si>
+    <t>Keyboard submit</t>
+  </si>
+  <si>
+    <t>Redirect to dashboard</t>
+  </si>
+  <si>
+    <t>Error message: Invalid email or password</t>
+  </si>
+  <si>
+    <t>1. Leave email blank
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Leave password blank
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Enter email without @
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Enter malformed email
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Enter wrong password
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Enter unregistered email
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Enter uppercase email
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Enter email with trailing space
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Enter password with leading space
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Enter SQL in email
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Enter script tag
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Try login
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Submit HTML email
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>Email: verylongemail...@example.com, Password: Valid123</t>
+  </si>
+  <si>
+    <t>1. Submit long email
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Paste email
+2. Enter password
+3. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Paste password
+2. Click Sign In</t>
+  </si>
+  <si>
+    <t>1. Click icon
+2. See password
+3. Click Sign In</t>
+  </si>
+  <si>
+    <t>Feature 02: User Management</t>
+  </si>
+  <si>
+    <t>Email: customer@practicesoftwaretesting.com 
+Password: welcome01</t>
+  </si>
+  <si>
+    <t>Email: admin@practicesoftwaretesting.com 
+Password: welcome01</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>User Sign In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> feature enables registered users to authenticate and access the system via a dedicated Sign In page with a form requiring a valid email and password. Upon submission, the system verifies credentials against the database, logging in valid users and redirecting them to a role-based dashboard with a welcome message. It includes real-time validation for email format and non-empty fields, plus error handling for invalid inputs or system issues, ensuring a secure and user-friendly experience.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>User Management</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> feature, exclusive to administrators with Admin privileges, allows managing user accounts by viewing a comprehensive user list, adding new accounts, editing details, deleting accounts, and resetting passwords. Integrated into the Admin dashboard, it offers an intuitive interface with a searchable, sortable user table and forms for user updates. The system ensures data integrity and security through input validation, unique email constraints, role-based access controls, and feedback via success or error messages.</t>
+    </r>
+  </si>
+  <si>
+    <t>View user list</t>
+  </si>
+  <si>
+    <t>Admin logged in</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>User table displayed</t>
+  </si>
+  <si>
+    <t>Add user - all valid</t>
+  </si>
+  <si>
+    <t>Admin adds user</t>
+  </si>
+  <si>
+    <t>Name: A, Email: a@e.com</t>
+  </si>
+  <si>
+    <t>User added</t>
+  </si>
+  <si>
+    <t>Add user - missing name</t>
+  </si>
+  <si>
+    <t>No name</t>
+  </si>
+  <si>
+    <t>Inline error: Name required</t>
+  </si>
+  <si>
+    <t>Add user - invalid email</t>
+  </si>
+  <si>
+    <t>Email: a.com</t>
+  </si>
+  <si>
+    <t>Add user - existing email</t>
+  </si>
+  <si>
+    <t>Email already exists</t>
+  </si>
+  <si>
+    <t>Same email</t>
+  </si>
+  <si>
+    <t>Error: Email exists</t>
+  </si>
+  <si>
+    <t>Add admin role</t>
+  </si>
+  <si>
+    <t>Admin adds another</t>
+  </si>
+  <si>
+    <t>Role: Admin</t>
+  </si>
+  <si>
+    <t>User added with Admin role</t>
+  </si>
+  <si>
+    <t>Edit user - change role</t>
+  </si>
+  <si>
+    <t>Admin edits user</t>
+  </si>
+  <si>
+    <t>Change: User → Admin</t>
+  </si>
+  <si>
+    <t>Update successful</t>
+  </si>
+  <si>
+    <t>Edit user - invalid email</t>
+  </si>
+  <si>
+    <t>Admin editing</t>
+  </si>
+  <si>
+    <t>Invalid email</t>
+  </si>
+  <si>
+    <t>Delete user - confirm</t>
+  </si>
+  <si>
+    <t>Admin wants to delete</t>
+  </si>
+  <si>
+    <t>Click delete</t>
+  </si>
+  <si>
+    <t>User removed</t>
+  </si>
+  <si>
+    <t>Delete user - cancel</t>
+  </si>
+  <si>
+    <t>Admin starts delete</t>
+  </si>
+  <si>
+    <t>Cancel dialog</t>
+  </si>
+  <si>
+    <t>User still exists</t>
+  </si>
+  <si>
+    <t>Reset password</t>
+  </si>
+  <si>
+    <t>Admin clicks reset</t>
+  </si>
+  <si>
+    <t>Target user</t>
+  </si>
+  <si>
+    <t>Password reset email sent</t>
+  </si>
+  <si>
+    <t>Access by regular user</t>
+  </si>
+  <si>
+    <t>Non-admin logged in</t>
+  </si>
+  <si>
+    <t>403 denied</t>
+  </si>
+  <si>
+    <t>Search by name</t>
+  </si>
+  <si>
+    <t>Admin on list</t>
+  </si>
+  <si>
+    <t>Name: John</t>
+  </si>
+  <si>
+    <t>Matching users shown</t>
+  </si>
+  <si>
+    <t>Add user - long name</t>
+  </si>
+  <si>
+    <t>Admin form</t>
+  </si>
+  <si>
+    <t>Name &gt; 100 chars</t>
+  </si>
+  <si>
+    <t>Error: Name too long</t>
+  </si>
+  <si>
+    <t>Reload during form</t>
+  </si>
+  <si>
+    <t>Editing user</t>
+  </si>
+  <si>
+    <t>Refresh page</t>
+  </si>
+  <si>
+    <t>Changes lost</t>
+  </si>
+  <si>
+    <t>Edit status only</t>
+  </si>
+  <si>
+    <t>Admin changes status</t>
+  </si>
+  <si>
+    <t>Status updated</t>
+  </si>
+  <si>
+    <t>1. Go to /admin/users</t>
+  </si>
+  <si>
+    <t>1. Click 'Add User'
+2. Fill in name and valid email
+3. Click 'Submit'</t>
+  </si>
+  <si>
+    <t>1. Click 'Add User'
+2. Leave name blank
+3. Click 'Submit'</t>
+  </si>
+  <si>
+    <t>1. Click 'Add User'
+2. Enter invalid email
+3. Click 'Submit'</t>
+  </si>
+  <si>
+    <t>1. Add user with existing email
+2. Click 'Submit'</t>
+  </si>
+  <si>
+    <t>1. Click 'Add User'
+2. Select role 'Admin'
+3. Submit</t>
+  </si>
+  <si>
+    <t>1. Click 'Edit'
+2. Change role
+3. Submit</t>
+  </si>
+  <si>
+    <t>1. Click 'Edit'
+2. Enter invalid email
+3. Submit</t>
+  </si>
+  <si>
+    <t>1. Click 'Delete'
+2. Confirm</t>
+  </si>
+  <si>
+    <t>1. Click 'Delete'
+2. Cancel</t>
+  </si>
+  <si>
+    <t>1. Click 'Reset Password'</t>
+  </si>
+  <si>
+    <t>1. Log in as non-admin
+2. Access /admin/users</t>
+  </si>
+  <si>
+    <t>1. Enter name into search bar
+2. Click 'Search'</t>
+  </si>
+  <si>
+    <t>1. Enter long name
 2. Submit</t>
   </si>
   <si>
-    <t>System either sanitizes input or blocks emojis</t>
-  </si>
-  <si>
-    <t>Rapid toggling of password visibility</t>
-  </si>
-  <si>
-    <t>User is on the registration form with password field</t>
-  </si>
-  <si>
-    <t>Click show/hide password icon repeatedly</t>
-  </si>
-  <si>
-    <t>1. Toggle password visibility multiple times</t>
-  </si>
-  <si>
-    <t>Password field functions correctly, no UI glitches</t>
-  </si>
-  <si>
-    <t>Registration with valid but uncommon email domain</t>
-  </si>
-  <si>
-    <t>Use email like user@protonmail.ch or user@uni.edu.vn</t>
-  </si>
-  <si>
-    <t>1. Fill full form with uncommon domain email
+    <t>1. Edit user
+2. Refresh browser</t>
+  </si>
+  <si>
+    <t>1. Click 'Edit'
+2. Toggle status
+3. Submit</t>
+  </si>
+  <si>
+    <t>Edit user - remove email</t>
+  </si>
+  <si>
+    <t>Admin editing user</t>
+  </si>
+  <si>
+    <t>Remove email field</t>
+  </si>
+  <si>
+    <t>1. Click 'Edit' on a user
+2. Clear email field
+3. Submit</t>
+  </si>
+  <si>
+    <t>Inline error: Email required</t>
+  </si>
+  <si>
+    <t>Edit user - change name only</t>
+  </si>
+  <si>
+    <t>Change name field</t>
+  </si>
+  <si>
+    <t>1. Click 'Edit'
+2. Modify name only
+3. Submit</t>
+  </si>
+  <si>
+    <t>User updated with new name</t>
+  </si>
+  <si>
+    <t>Search by invalid input</t>
+  </si>
+  <si>
+    <t>Admin on user page</t>
+  </si>
+  <si>
+    <t>Search: !@#$%^&amp;*</t>
+  </si>
+  <si>
+    <t>1. Enter invalid search term
+2. Click Search</t>
+  </si>
+  <si>
+    <t>No users displayed or validation shown</t>
+  </si>
+  <si>
+    <t>Search by partial email</t>
+  </si>
+  <si>
+    <t>Email contains 'practice'</t>
+  </si>
+  <si>
+    <t>1. Enter partial email
+2. Click Search</t>
+  </si>
+  <si>
+    <t>Cancel user creation</t>
+  </si>
+  <si>
+    <t>Admin starts adding user</t>
+  </si>
+  <si>
+    <t>Enter form data</t>
+  </si>
+  <si>
+    <t>1. Click 'Add User'
+2. Fill in fields
+3. Click 'Cancel'</t>
+  </si>
+  <si>
+    <t>Form closes, no user added</t>
+  </si>
+  <si>
+    <t>Case-insensitive email check</t>
+  </si>
+  <si>
+    <t>Email in different case</t>
+  </si>
+  <si>
+    <t>1. Add email: CUSTOMER@practicesoftwaretesting.com
 2. Submit</t>
   </si>
   <si>
-    <t>Registration succeeds, domain accepted</t>
-  </si>
-  <si>
-    <t>Attempt SQL injection in form fields</t>
-  </si>
-  <si>
-    <t>Enter `' OR '1'='1` in name or email</t>
-  </si>
-  <si>
-    <t>1. Fill form with malicious input
+    <t>Error: Email already exists</t>
+  </si>
+  <si>
+    <t>Edit user with no changes</t>
+  </si>
+  <si>
+    <t>Submit without changes</t>
+  </si>
+  <si>
+    <t>1. Click 'Edit'
+2. Submit unchanged form</t>
+  </si>
+  <si>
+    <t>Success or warning: no changes detected</t>
+  </si>
+  <si>
+    <t>Add user with max-length email</t>
+  </si>
+  <si>
+    <t>Email ~100 chars</t>
+  </si>
+  <si>
+    <t>1. Fill form with long but valid email
 2. Submit</t>
   </si>
   <si>
-    <t>System blocks input; account not created</t>
-  </si>
-  <si>
-    <t>Form reset after submission</t>
-  </si>
-  <si>
-    <t>User has submitted the registration form</t>
-  </si>
-  <si>
-    <t>Check state of form after success</t>
-  </si>
-  <si>
-    <t>1. Fill form
-2. Submit
-3. Observe field states</t>
-  </si>
-  <si>
-    <t>Form fields reset to empty, ready for new input</t>
-  </si>
-  <si>
-    <t>Login section appears</t>
-  </si>
-  <si>
-    <t>Continue to the next step</t>
-  </si>
-  <si>
-    <t>Confirm button is disable</t>
-  </si>
-  <si>
-    <t>Guest user attempts checkout without signing in</t>
-  </si>
-  <si>
-    <t>Guest user (not logged in), 1 item in cart</t>
-  </si>
-  <si>
-    <t>Cart: quantity=1, Item="Combination Pliers"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	1.	Open cart page
-	2.	Verify item exists in cart
-	3.	Click Proceed to Billing Address</t>
-  </si>
-  <si>
-    <t>System redirects to Sign in page, message displayed: "Please sign in to proceed"</t>
-  </si>
-  <si>
-    <t>Logged-in user skips sign in and proceeds to billing</t>
-  </si>
-  <si>
-    <t>User is already signed in, 1 item in cart</t>
-  </si>
-  <si>
-    <t>1.	Open cart page
-	2.	Verify user is signed in
-	3.	Click Proceed to Billing Address</t>
-  </si>
-  <si>
-    <t>Redirects directly to Billing Address step without sign-in prompt</t>
-  </si>
-  <si>
-    <t>Valid Bank Transfer</t>
-  </si>
-  <si>
-    <t>User is logged in, 1 item in cart, billing completed</t>
-  </si>
-  <si>
-    <t>Cart: quantity=1, Item="Combination Pliers"; Billing: Street="Test Street 98", City="Vienna", Country="Austria"; Payment: Bank Name="Test Bank", Account Name="Jane Doe", Account Number="1234567890"</t>
-  </si>
-  <si>
-    <t>1. Click Proceed to Billing Address. 
-2. Enter Street="Test Street 98", City="Vienna", Country="Austria". 
-3. Click Proceed to Payment. 
-4. Select "Bank Transfer" from dropdown. 
-5. Enter Bank Name="Test Bank", Account Name="Jane Doe", Account Number="1234567890". 
-6. Click Confirm.</t>
-  </si>
-  <si>
-    <t>Checkout process completes successfully with order confirmation displayed</t>
-  </si>
-  <si>
-    <t>Empty Bank Name</t>
-  </si>
-  <si>
-    <t>Cart: quantity=1, Item="Combination Pliers"; Billing: Street="Test Street 98", City="Vienna", Country="Austria"; Payment: Bank Name="", Account Name="Jane Doe", Account Number="1234567890"</t>
-  </si>
-  <si>
-    <t>1. Click Proceed to Billing Address. 
-2. Enter Street="Test Street 98", City="Vienna", Country="Austria". 
-3. Click Proceed to Payment. 
-4. Select "Bank Transfer" from dropdown. 
-5. Enter Bank Name="", Account Name="Jane Doe", Account Number="1234567890". 
-6. Click Confirm.</t>
-  </si>
-  <si>
-    <t>Error message "Bank Name is required" is displayed, remains on Payment step</t>
-  </si>
-  <si>
-    <t>Bank Name with numbers</t>
-  </si>
-  <si>
-    <t>Cart: quantity=1, Item="Combination Pliers"; Billing: Street="Test Street 98", City="Vienna", Country="Austria"; Payment: Bank Name="Test Bank 123", Account Name="Jane Doe", Account Number="1234567890"</t>
-  </si>
-  <si>
-    <t>1. Click Proceed to Billing Address. 
-2. Enter Street="Test Street 98", City="Vienna", Country="Austria". 
-3. Click Proceed to Payment. 
-4. Select "Bank Transfer" from dropdown. 
-5. Enter Bank Name="Test Bank 123", Account Name="Jane Doe", Account Number="1234567890". 
-6. Click Confirm.</t>
-  </si>
-  <si>
-    <t>Error message "Bank Name must contain only letters and spaces" is displayed, remains on Payment step</t>
-  </si>
-  <si>
-    <t>Payment successful</t>
-  </si>
-  <si>
-    <t>Empty Account Number</t>
-  </si>
-  <si>
-    <t>Cart: quantity=1, Item="Combination Pliers"; Billing: Street="Test Street 98", City="Vienna", Country="Austria"; Payment: Bank Name="Test Bank", Account Name="Jane Doe", Account Number=""</t>
-  </si>
-  <si>
-    <t>1. Click Proceed to Billing Address. 
-2. Enter Street="Test Street 98", City="Vienna", Country="Austria". 
-3. Click Proceed to Payment. 
-4. Select "Bank Transfer" from dropdown. 
-5. Enter Bank Name="Test Bank", Account Name="Jane Doe", Account Number="". 
-6. Click Confirm.</t>
-  </si>
-  <si>
-    <t>Error message "Accouont Number is required" is displayed, remains on Payment step</t>
-  </si>
-  <si>
-    <t>Account Number with letters</t>
-  </si>
-  <si>
-    <t>Cart: quantity=1, Item="Combination Pliers"; Billing: Street="Test Street 98", City="Vienna", Country="Austria"; Payment: Bank Name="Test Bank", Account Name="Jane Doe", Account Number="123abc"</t>
-  </si>
-  <si>
-    <t>1. Click Proceed to Billing Address. 
-2. Enter Street="Test Street 98", City="Vienna", Country="Austria". 
-3. Click Proceed to Payment. 
-4. Select "Bank Transfer" from dropdown. 
-5. Enter Bank Name="Test Bank", Account Name="Jane Doe", Account Number="123abc". 
-6. Click Confirm.</t>
-  </si>
-  <si>
-    <t>Error message "Account Number must be numeric" is displayed, remains on Payment step</t>
-  </si>
-  <si>
-    <t>Cart: quantity=1, Item="Combination Pliers"; Billing: Street="Test Street 98", City="Vienna", Country="Austria"; Payment: NO selected metohd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Proceed to Billing Address. 
-2. Enter Street="Test Street 98", City="Vienna", Country="Austria". 
-3. Click Proceed to Payment. </t>
-  </si>
-  <si>
-    <t>Proceed to Confirm button is disable</t>
-  </si>
-  <si>
-    <t>Select Credit Card in payment method</t>
-  </si>
-  <si>
-    <t>Cart: quantity=1, Item="Combination Pliers"; Billing: Street="Test Street 98", City="Vienna", Country="Austria"; Payment: Credit Card</t>
-  </si>
-  <si>
-    <t>Display input fields for Credit Card info (card number, date, …)</t>
-  </si>
-  <si>
-    <t>Display input fields for Bank Transfer</t>
-  </si>
-  <si>
-    <t>Select Cash on Delivery in payment method</t>
-  </si>
-  <si>
-    <t>Cart: quantity=1, Item="Combination Pliers"; Billing: Street="Test Street 98", City="Vienna", Country="Austria"; Payment: Gift Card</t>
-  </si>
-  <si>
-    <t>Confirm button enable</t>
-  </si>
-  <si>
-    <t>Select Gift Card in payment method</t>
-  </si>
-  <si>
-    <t>Display input fields for Gift Card info (code, valid date, …)</t>
-  </si>
-  <si>
-    <t>Select Buy Now Pay Later in payment method</t>
-  </si>
-  <si>
-    <t>Display input fields for Buy Now Pay Later info (card, valid date, …)</t>
-  </si>
-  <si>
-    <t>Invalid quantity (0) of item in cart</t>
-  </si>
-  <si>
-    <t>User is logged in, 1 item in cart</t>
-  </si>
-  <si>
-    <t>Cart: quantity=0, Item="Combination Pliers"</t>
-  </si>
-  <si>
-    <t>1. Set quantity to 0 for the item. 
-2. Click Proceed to Checkout.</t>
-  </si>
-  <si>
-    <t>Error message "Quantity must be at least 1" is displayed, checkout halted</t>
-  </si>
-  <si>
-    <t>Checkout process continues with the next step</t>
-  </si>
-  <si>
-    <t>Checkout with negative quantity (-1)</t>
-  </si>
-  <si>
-    <t>Cart: quantity=-1, Item="Combination Pliers"</t>
-  </si>
-  <si>
-    <t>Invalid quantity (non-numeric) of item in cart</t>
-  </si>
-  <si>
-    <t>Cart: quantity="abc", Item="Combination Pliers"</t>
-  </si>
-  <si>
-    <t>1. Set quantity to "abc" for the item. 
-2. Click Proceed to Checkout.</t>
-  </si>
-  <si>
-    <t>Error message "Quantity must be numeric" is displayed, checkout halted</t>
-  </si>
-  <si>
-    <t>Item with empty quantity in cart</t>
-  </si>
-  <si>
-    <t>Cart: quantity="", Item="Combination Pliers"</t>
-  </si>
-  <si>
-    <t>1. Set quantity to "" for the item. 
-2. Click Proceed to Checkout.</t>
-  </si>
-  <si>
-    <t>Remove item from cart</t>
-  </si>
-  <si>
-    <t>1. Click Remove button for the item. 
-2. Verify cart contents.</t>
-  </si>
-  <si>
-    <t>Cart is empty, Proceed to Checkout button is disabled</t>
-  </si>
-  <si>
-    <t>Can not remove item in cart by remove button</t>
+    <t>Error message: (blank)</t>
+  </si>
+  <si>
+    <t>Can not add user with admin role</t>
+  </si>
+  <si>
+    <t>Error message: Invalid email</t>
+  </si>
+  <si>
+    <t>Error message: Seems like this customer is used elsewhere.</t>
+  </si>
+  <si>
+    <t>Can not reset password</t>
+  </si>
+  <si>
+    <t>404 denied</t>
+  </si>
+  <si>
+    <t>Enable</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yy"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -841,7 +1039,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -862,11 +1060,21 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -874,6 +1082,20 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1043,20 +1265,6 @@
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1083,20 +1291,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1" displayName="Table1" ref="A1:L51" totalsRowShown="0" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1" displayName="Table1" ref="A1:L48" totalsRowShown="0" dataDxfId="0">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Feature ID" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Test case ID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Title" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{FC56E23B-B122-0441-B866-05DF8E70288F}" name="Preconditions" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{AB46A491-07AE-F943-A23C-EA24440BDC6F}" name="Inputs" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Test Steps" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Expected Result" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Actual Result" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Status" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Tester" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Tested Date" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Remark" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Feature ID" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Test case ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Title" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{FC56E23B-B122-0441-B866-05DF8E70288F}" name="Preconditions" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{AB46A491-07AE-F943-A23C-EA24440BDC6F}" name="Inputs" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Test Steps" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Expected Result" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Actual Result" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Status" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Tester" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Tested Date" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Remark" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1416,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -1433,18 +1641,18 @@
         <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="130" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1457,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
@@ -1468,13 +1676,14 @@
     <col min="6" max="6" width="33.1640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="27.6640625" style="2" customWidth="1"/>
     <col min="8" max="8" width="25.83203125" customWidth="1"/>
-    <col min="9" max="10" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" customWidth="1"/>
     <col min="11" max="11" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
         <v>11</v>
@@ -1511,8 +1720,8 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>119</v>
+      <c r="A2" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1526,36 +1735,36 @@
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K3" s="7">
         <v>45825</v>
@@ -1563,35 +1772,35 @@
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K4" s="7">
         <v>45825</v>
@@ -1599,35 +1808,35 @@
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>6</v>
+        <v>118</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K5" s="7">
         <v>45825</v>
@@ -1635,35 +1844,35 @@
       <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>6</v>
+        <v>118</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K6" s="7">
         <v>45825</v>
@@ -1671,35 +1880,35 @@
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>49</v>
+        <v>118</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K7" s="7">
         <v>45825</v>
@@ -1707,35 +1916,35 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>6</v>
+        <v>118</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K8" s="7">
         <v>45825</v>
@@ -1743,35 +1952,35 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>6</v>
+        <v>118</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K9" s="7">
         <v>45825</v>
@@ -1779,35 +1988,35 @@
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>49</v>
+        <v>118</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K10" s="7">
         <v>45825</v>
@@ -1815,35 +2024,35 @@
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>53</v>
+        <v>125</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>6</v>
+        <v>118</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K11" s="7">
         <v>45825</v>
@@ -1851,107 +2060,107 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K12" s="7">
         <v>45825</v>
       </c>
-      <c r="L12" s="9"/>
+      <c r="L12" s="8"/>
     </row>
     <row r="13" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K13" s="7">
         <v>45825</v>
       </c>
-      <c r="L13" s="10"/>
+      <c r="L13" s="9"/>
     </row>
     <row r="14" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>6</v>
+        <v>118</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K14" s="7">
         <v>45825</v>
@@ -1959,35 +2168,35 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>49</v>
+        <v>118</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K15" s="7">
         <v>45825</v>
@@ -1995,35 +2204,35 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>6</v>
+        <v>118</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K16" s="7">
         <v>45825</v>
@@ -2031,1238 +2240,1143 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>6</v>
+        <v>118</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K17" s="7">
         <v>45825</v>
       </c>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>49</v>
+        <v>118</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K18" s="7">
         <v>45825</v>
       </c>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+    </row>
+    <row r="19" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>6</v>
+        <v>118</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K19" s="7">
         <v>45825</v>
       </c>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+    </row>
+    <row r="20" spans="1:12" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K20" s="7">
         <v>45825</v>
       </c>
-      <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K21" s="7">
         <v>45825</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:12" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>49</v>
+        <v>112</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K22" s="7">
         <v>45825</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K23" s="7">
         <v>45825</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I24" s="5" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+    </row>
+    <row r="25" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I25" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K24" s="7">
-        <v>45825</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K25" s="7">
         <v>45825</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>7</v>
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K26" s="7">
         <v>45825</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-    </row>
-    <row r="28" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K27" s="7">
+        <v>45825</v>
+      </c>
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>97</v>
+        <v>203</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>6</v>
+        <v>43</v>
+      </c>
+      <c r="H28" t="s">
+        <v>249</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K28" s="7">
         <v>45825</v>
       </c>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>6</v>
+        <v>149</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K29" s="7">
         <v>45825</v>
       </c>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>102</v>
+        <v>161</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>97</v>
+        <v>205</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I30" t="s">
-        <v>49</v>
+        <v>162</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K30" s="7">
         <v>45825</v>
       </c>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K31" s="7">
         <v>45825</v>
       </c>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>95</v>
+        <v>168</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>97</v>
+        <v>207</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I32" t="s">
-        <v>49</v>
+        <v>251</v>
+      </c>
+      <c r="H32" t="s">
+        <v>249</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K32" s="7">
         <v>45825</v>
       </c>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>95</v>
+        <v>171</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>97</v>
+        <v>208</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>6</v>
+        <v>252</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K33" s="7">
         <v>45825</v>
       </c>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E34" t="s">
-        <v>148</v>
+        <v>175</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>149</v>
+        <v>209</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>6</v>
+        <v>252</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K34" s="7">
         <v>45825</v>
       </c>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E35" t="s">
-        <v>148</v>
+        <v>179</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>153</v>
+        <v>210</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>6</v>
+        <v>181</v>
+      </c>
+      <c r="H35" t="s">
+        <v>253</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K35" s="7">
         <v>45825</v>
       </c>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="1:12" ht="144" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>158</v>
+        <v>211</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>159</v>
+        <v>254</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K36" s="7">
         <v>45825</v>
       </c>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="1:12" ht="144" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>162</v>
+        <v>212</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K37" s="7">
         <v>45825</v>
       </c>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="1:12" ht="144" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>49</v>
+        <v>149</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K38" s="7">
         <v>45825</v>
       </c>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="1:12" ht="128" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>171</v>
+        <v>214</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K39" s="7">
         <v>45825</v>
       </c>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="1:12" ht="144" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>174</v>
+        <v>255</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>49</v>
+        <v>199</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K40" s="7">
         <v>45825</v>
       </c>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>110</v>
+        <v>216</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K41" s="7">
         <v>45825</v>
       </c>
-      <c r="L41" s="2"/>
-    </row>
-    <row r="42" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>49</v>
+        <v>224</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K42" s="7">
         <v>45825</v>
       </c>
-      <c r="L42" s="2"/>
-    </row>
-    <row r="43" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="L42" s="13"/>
+    </row>
+    <row r="43" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>49</v>
+        <v>229</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K43" s="7">
         <v>45825</v>
       </c>
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="L43" s="13"/>
+    </row>
+    <row r="44" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>178</v>
+        <v>232</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>188</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>49</v>
+        <v>188</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K44" s="7">
         <v>45825</v>
       </c>
-      <c r="L44" s="2"/>
-    </row>
-    <row r="45" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="L44" s="13"/>
+    </row>
+    <row r="45" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>156</v>
+        <v>234</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>181</v>
+        <v>235</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>49</v>
+        <v>237</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K45" s="7">
         <v>45825</v>
       </c>
-      <c r="L45" s="2"/>
-    </row>
-    <row r="46" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="L45" s="13"/>
+    </row>
+    <row r="46" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>112</v>
+        <v>238</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>114</v>
+        <v>239</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>115</v>
+        <v>240</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>116</v>
+        <v>241</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>6</v>
+        <v>149</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K46" s="7">
         <v>45825</v>
       </c>
-      <c r="L46" s="2"/>
-    </row>
-    <row r="47" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="L46" s="13"/>
+    </row>
+    <row r="47" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D47" t="s">
-        <v>192</v>
-      </c>
-      <c r="E47" t="s">
-        <v>193</v>
+        <v>242</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>49</v>
+        <v>245</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K47" s="7">
         <v>45825</v>
       </c>
-      <c r="L47" s="2"/>
-    </row>
-    <row r="48" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="L47" s="13"/>
+    </row>
+    <row r="48" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D48" t="s">
-        <v>192</v>
-      </c>
-      <c r="E48" t="s">
-        <v>198</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K48" s="7">
         <v>45825</v>
       </c>
-      <c r="L48" s="2"/>
-    </row>
-    <row r="49" spans="1:12" ht="48" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D49" t="s">
-        <v>192</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K49" s="7">
-        <v>45825</v>
-      </c>
-      <c r="L49" s="2"/>
-    </row>
-    <row r="50" spans="1:12" ht="48" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D50" t="s">
-        <v>192</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K50" s="7">
-        <v>45825</v>
-      </c>
-      <c r="L50" s="2"/>
-    </row>
-    <row r="51" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D51" t="s">
-        <v>192</v>
-      </c>
-      <c r="E51" t="s">
-        <v>148</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K51" s="7">
-        <v>45825</v>
-      </c>
-      <c r="L51" s="2"/>
+      <c r="L48" s="13"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A49" s="13"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
